--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3099,32 +3099,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134673097</v>
+        <v>135141304</v>
       </c>
       <c r="B26" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3137,13 +3137,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455100</v>
+        <v>455021</v>
       </c>
       <c r="R26" t="n">
-        <v>6795418</v>
+        <v>6795446</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3167,12 +3167,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3200,32 +3200,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134673122</v>
+        <v>135141324</v>
       </c>
       <c r="B27" t="n">
-        <v>80488</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3234,17 +3234,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455113</v>
+        <v>455053</v>
       </c>
       <c r="R27" t="n">
-        <v>6795465</v>
+        <v>6795452</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3268,12 +3268,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3301,56 +3301,51 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134614537</v>
+        <v>135141340</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455028</v>
+        <v>454969</v>
       </c>
       <c r="R28" t="n">
-        <v>6795330</v>
+        <v>6795402</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3374,12 +3369,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3388,6 +3383,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3406,10 +3402,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134626925</v>
+        <v>134673097</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3417,42 +3413,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454878</v>
+        <v>455100</v>
       </c>
       <c r="R29" t="n">
-        <v>6795300</v>
+        <v>6795418</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3479,12 +3470,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3493,6 +3484,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3511,10 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134627054</v>
+        <v>134673122</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3522,31 +3514,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3554,10 +3541,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454812</v>
+        <v>455113</v>
       </c>
       <c r="R30" t="n">
-        <v>6795344</v>
+        <v>6795465</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3584,12 +3571,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3598,6 +3585,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3616,10 +3604,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134627301</v>
+        <v>135141238</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3627,45 +3615,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454942</v>
+        <v>455104</v>
       </c>
       <c r="R31" t="n">
-        <v>6795417</v>
+        <v>6795429</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3689,12 +3672,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3703,6 +3686,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3721,7 +3705,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134673183</v>
+        <v>134614537</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3760,14 +3744,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455102</v>
+        <v>455028</v>
       </c>
       <c r="R32" t="n">
-        <v>6795356</v>
+        <v>6795330</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3794,12 +3778,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3826,7 +3810,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134673244</v>
+        <v>134626925</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -3859,20 +3843,20 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455111</v>
+        <v>454878</v>
       </c>
       <c r="R33" t="n">
-        <v>6795338</v>
+        <v>6795300</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3899,12 +3883,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3931,7 +3915,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134673280</v>
+        <v>134627054</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -3974,10 +3958,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455026</v>
+        <v>454812</v>
       </c>
       <c r="R34" t="n">
-        <v>6795364</v>
+        <v>6795344</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4004,12 +3988,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4036,7 +4020,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134673340</v>
+        <v>134627301</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4079,10 +4063,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455035</v>
+        <v>454942</v>
       </c>
       <c r="R35" t="n">
-        <v>6795361</v>
+        <v>6795417</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4109,12 +4093,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4141,7 +4125,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134673359</v>
+        <v>134673183</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4174,7 +4158,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4184,10 +4168,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455183</v>
+        <v>455102</v>
       </c>
       <c r="R36" t="n">
-        <v>6795468</v>
+        <v>6795356</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4246,38 +4230,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134614645</v>
+        <v>134673244</v>
       </c>
       <c r="B37" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4285,10 +4273,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455028</v>
+        <v>455111</v>
       </c>
       <c r="R37" t="n">
-        <v>6795377</v>
+        <v>6795338</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4315,12 +4303,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4329,7 +4317,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4348,49 +4335,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134614705</v>
+        <v>134673280</v>
       </c>
       <c r="B38" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455116</v>
+        <v>455026</v>
       </c>
       <c r="R38" t="n">
-        <v>6795394</v>
+        <v>6795364</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4417,12 +4408,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4431,7 +4422,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4450,38 +4440,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134614735</v>
+        <v>134673340</v>
       </c>
       <c r="B39" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4489,10 +4483,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455163</v>
+        <v>455035</v>
       </c>
       <c r="R39" t="n">
-        <v>6795351</v>
+        <v>6795361</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4519,12 +4513,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4533,7 +4527,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4552,38 +4545,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134614754</v>
+        <v>134673359</v>
       </c>
       <c r="B40" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4591,10 +4588,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455159</v>
+        <v>455183</v>
       </c>
       <c r="R40" t="n">
-        <v>6795377</v>
+        <v>6795468</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4621,12 +4618,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4635,7 +4632,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4654,7 +4650,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134627237</v>
+        <v>134614645</v>
       </c>
       <c r="B41" t="n">
         <v>99112</v>
@@ -4693,10 +4689,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454916</v>
+        <v>455028</v>
       </c>
       <c r="R41" t="n">
-        <v>6795349</v>
+        <v>6795377</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4756,10 +4752,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134614906</v>
+        <v>134614705</v>
       </c>
       <c r="B42" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4767,21 +4763,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4791,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455317</v>
+        <v>455116</v>
       </c>
       <c r="R42" t="n">
-        <v>6795637</v>
+        <v>6795394</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4858,10 +4854,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134627179</v>
+        <v>134614735</v>
       </c>
       <c r="B43" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,21 +4865,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4893,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454911</v>
+        <v>455163</v>
       </c>
       <c r="R43" t="n">
-        <v>6795314</v>
+        <v>6795351</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4960,10 +4956,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134627242</v>
+        <v>134614754</v>
       </c>
       <c r="B44" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4971,21 +4967,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4995,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454916</v>
+        <v>455159</v>
       </c>
       <c r="R44" t="n">
-        <v>6795349</v>
+        <v>6795377</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5062,10 +5058,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134627258</v>
+        <v>134627237</v>
       </c>
       <c r="B45" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5073,21 +5069,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5097,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454930</v>
+        <v>454916</v>
       </c>
       <c r="R45" t="n">
-        <v>6795363</v>
+        <v>6795349</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5164,10 +5160,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134614664</v>
+        <v>134614906</v>
       </c>
       <c r="B46" t="n">
-        <v>99217</v>
+        <v>99099</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5175,21 +5171,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5199,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455110</v>
+        <v>455317</v>
       </c>
       <c r="R46" t="n">
-        <v>6795376</v>
+        <v>6795637</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5266,10 +5262,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134614688</v>
+        <v>134627179</v>
       </c>
       <c r="B47" t="n">
-        <v>99217</v>
+        <v>109924</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5277,21 +5273,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>221184</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5305,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455116</v>
+        <v>454911</v>
       </c>
       <c r="R47" t="n">
-        <v>6795380</v>
+        <v>6795314</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5368,10 +5364,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134614788</v>
+        <v>134627242</v>
       </c>
       <c r="B48" t="n">
-        <v>99217</v>
+        <v>109924</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5379,21 +5375,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>221184</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5403,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455170</v>
+        <v>454916</v>
       </c>
       <c r="R48" t="n">
-        <v>6795392</v>
+        <v>6795349</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5470,10 +5466,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134614819</v>
+        <v>134627258</v>
       </c>
       <c r="B49" t="n">
-        <v>99217</v>
+        <v>109924</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5481,21 +5477,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>221184</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5505,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455188</v>
+        <v>454930</v>
       </c>
       <c r="R49" t="n">
-        <v>6795401</v>
+        <v>6795363</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5572,7 +5568,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134614899</v>
+        <v>134614664</v>
       </c>
       <c r="B50" t="n">
         <v>99217</v>
@@ -5611,10 +5607,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455327</v>
+        <v>455110</v>
       </c>
       <c r="R50" t="n">
-        <v>6795641</v>
+        <v>6795376</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5674,7 +5670,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134627270</v>
+        <v>134614688</v>
       </c>
       <c r="B51" t="n">
         <v>99217</v>
@@ -5713,10 +5709,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454933</v>
+        <v>455116</v>
       </c>
       <c r="R51" t="n">
-        <v>6795362</v>
+        <v>6795380</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5773,6 +5769,516 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134614788</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>455170</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6795392</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134614819</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>455188</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6795401</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134614899</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>455327</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6795641</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134627270</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>454933</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6795362</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135141343</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>454969</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6795402</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614586</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614602</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614617</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614692</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614778</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614823</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614834</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614839</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614845</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614867</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614878</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614890</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614909</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614972</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614977</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614988</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627106</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627119</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627145</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627160</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627309</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627464</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673366</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141304</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141324</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141340</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673097</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3601,6 +3746,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673122</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3702,6 +3852,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141238</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3807,6 +3962,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614537</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3912,6 +4072,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134626925</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4017,6 +4182,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627054</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4122,6 +4292,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627301</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4227,6 +4402,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673183</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4332,6 +4512,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673244</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4437,6 +4622,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673280</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4542,6 +4732,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673340</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4647,6 +4842,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673359</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4749,6 +4949,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614645</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4851,6 +5056,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614705</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4953,6 +5163,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614735</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5055,6 +5270,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614754</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5157,6 +5377,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627237</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5259,6 +5484,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614906</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5361,6 +5591,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627179</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5463,6 +5698,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627242</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5565,6 +5805,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627258</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5667,6 +5912,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614664</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5769,6 +6019,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614688</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5871,6 +6126,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614788</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5973,6 +6233,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614819</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6075,6 +6340,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614899</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6177,6 +6447,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627270</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6279,8 +6554,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135141343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134614586</v>
+        <v>135613306</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,17 +820,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455034</v>
+        <v>455151</v>
       </c>
       <c r="R3" t="n">
-        <v>6795328</v>
+        <v>6795414</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,13 +886,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614586</t>
+          <t>https://artportalen.se/Sighting/135613306</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134614602</v>
+        <v>134614586</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -926,14 +926,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455012</v>
+        <v>455034</v>
       </c>
       <c r="R4" t="n">
-        <v>6795340</v>
+        <v>6795328</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,13 +992,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614602</t>
+          <t>https://artportalen.se/Sighting/134614586</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134614617</v>
+        <v>134614602</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455021</v>
+        <v>455012</v>
       </c>
       <c r="R5" t="n">
-        <v>6795317</v>
+        <v>6795340</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,13 +1098,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614617</t>
+          <t>https://artportalen.se/Sighting/134614602</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134614692</v>
+        <v>134614617</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455116</v>
+        <v>455021</v>
       </c>
       <c r="R6" t="n">
-        <v>6795380</v>
+        <v>6795317</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,13 +1204,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614692</t>
+          <t>https://artportalen.se/Sighting/134614617</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134614778</v>
+        <v>134614692</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455170</v>
+        <v>455116</v>
       </c>
       <c r="R7" t="n">
-        <v>6795392</v>
+        <v>6795380</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,13 +1310,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614778</t>
+          <t>https://artportalen.se/Sighting/134614692</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134614823</v>
+        <v>134614778</v>
       </c>
       <c r="B8" t="n">
         <v>79373</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455188</v>
+        <v>455170</v>
       </c>
       <c r="R8" t="n">
-        <v>6795401</v>
+        <v>6795392</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1416,13 +1416,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614823</t>
+          <t>https://artportalen.se/Sighting/134614778</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134614834</v>
+        <v>134614823</v>
       </c>
       <c r="B9" t="n">
         <v>79373</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455246</v>
+        <v>455188</v>
       </c>
       <c r="R9" t="n">
-        <v>6795421</v>
+        <v>6795401</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1522,13 +1522,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614834</t>
+          <t>https://artportalen.se/Sighting/134614823</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134614839</v>
+        <v>134614834</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455282</v>
+        <v>455246</v>
       </c>
       <c r="R10" t="n">
-        <v>6795462</v>
+        <v>6795421</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1628,13 +1628,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614839</t>
+          <t>https://artportalen.se/Sighting/134614834</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134614845</v>
+        <v>134614839</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455254</v>
+        <v>455282</v>
       </c>
       <c r="R11" t="n">
-        <v>6795551</v>
+        <v>6795462</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1734,13 +1734,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614845</t>
+          <t>https://artportalen.se/Sighting/134614839</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134614867</v>
+        <v>134614845</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455274</v>
+        <v>455254</v>
       </c>
       <c r="R12" t="n">
-        <v>6795546</v>
+        <v>6795551</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1840,13 +1840,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614867</t>
+          <t>https://artportalen.se/Sighting/134614845</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134614878</v>
+        <v>134614867</v>
       </c>
       <c r="B13" t="n">
         <v>79373</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455305</v>
+        <v>455274</v>
       </c>
       <c r="R13" t="n">
-        <v>6795540</v>
+        <v>6795546</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1946,13 +1946,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614878</t>
+          <t>https://artportalen.se/Sighting/134614867</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134614890</v>
+        <v>134614878</v>
       </c>
       <c r="B14" t="n">
         <v>79373</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455327</v>
+        <v>455305</v>
       </c>
       <c r="R14" t="n">
-        <v>6795641</v>
+        <v>6795540</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,13 +2052,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614890</t>
+          <t>https://artportalen.se/Sighting/134614878</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134614909</v>
+        <v>134614890</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455317</v>
+        <v>455327</v>
       </c>
       <c r="R15" t="n">
-        <v>6795637</v>
+        <v>6795641</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2158,13 +2158,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614909</t>
+          <t>https://artportalen.se/Sighting/134614890</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134614972</v>
+        <v>134614909</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455066</v>
+        <v>455317</v>
       </c>
       <c r="R16" t="n">
-        <v>6795462</v>
+        <v>6795637</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2264,13 +2264,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614972</t>
+          <t>https://artportalen.se/Sighting/134614909</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134614977</v>
+        <v>134614972</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455076</v>
+        <v>455066</v>
       </c>
       <c r="R17" t="n">
-        <v>6795492</v>
+        <v>6795462</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2370,13 +2370,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614977</t>
+          <t>https://artportalen.se/Sighting/134614972</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134614988</v>
+        <v>134614977</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455095</v>
+        <v>455076</v>
       </c>
       <c r="R18" t="n">
-        <v>6795496</v>
+        <v>6795492</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2476,13 +2476,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614988</t>
+          <t>https://artportalen.se/Sighting/134614977</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134627106</v>
+        <v>134614988</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2516,14 +2516,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454812</v>
+        <v>455095</v>
       </c>
       <c r="R19" t="n">
-        <v>6795344</v>
+        <v>6795496</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2582,13 +2582,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627106</t>
+          <t>https://artportalen.se/Sighting/134614988</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134627119</v>
+        <v>134627106</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454878</v>
+        <v>454812</v>
       </c>
       <c r="R20" t="n">
-        <v>6795300</v>
+        <v>6795344</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2688,13 +2688,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627119</t>
+          <t>https://artportalen.se/Sighting/134627106</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134627145</v>
+        <v>134627119</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454848</v>
+        <v>454878</v>
       </c>
       <c r="R21" t="n">
-        <v>6795313</v>
+        <v>6795300</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2794,13 +2794,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627145</t>
+          <t>https://artportalen.se/Sighting/134627119</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134627160</v>
+        <v>134627145</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2834,14 +2834,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454866</v>
+        <v>454848</v>
       </c>
       <c r="R22" t="n">
-        <v>6795380</v>
+        <v>6795313</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2900,13 +2900,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627160</t>
+          <t>https://artportalen.se/Sighting/134627145</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134627309</v>
+        <v>134627160</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454942</v>
+        <v>454866</v>
       </c>
       <c r="R23" t="n">
-        <v>6795417</v>
+        <v>6795380</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3006,13 +3006,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627309</t>
+          <t>https://artportalen.se/Sighting/134627160</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134627464</v>
+        <v>134627309</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454917</v>
+        <v>454942</v>
       </c>
       <c r="R24" t="n">
-        <v>6795398</v>
+        <v>6795417</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3112,13 +3112,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627464</t>
+          <t>https://artportalen.se/Sighting/134627309</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134673366</v>
+        <v>134627464</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455114</v>
+        <v>454917</v>
       </c>
       <c r="R25" t="n">
-        <v>6795450</v>
+        <v>6795398</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,13 +3218,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673366</t>
+          <t>https://artportalen.se/Sighting/134627464</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135141304</v>
+        <v>134673366</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455021</v>
+        <v>455114</v>
       </c>
       <c r="R26" t="n">
-        <v>6795446</v>
+        <v>6795450</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3324,16 +3324,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135141304</t>
+          <t>https://artportalen.se/Sighting/134673366</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135141324</v>
+        <v>135141304</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455053</v>
+        <v>455021</v>
       </c>
       <c r="R27" t="n">
-        <v>6795452</v>
+        <v>6795446</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,16 +3430,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135141324</t>
+          <t>https://artportalen.se/Sighting/135141304</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135141340</v>
+        <v>135141324</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454969</v>
+        <v>455053</v>
       </c>
       <c r="R28" t="n">
-        <v>6795402</v>
+        <v>6795452</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,38 +3536,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135141340</t>
+          <t>https://artportalen.se/Sighting/135141324</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134673097</v>
+        <v>135141340</v>
       </c>
       <c r="B29" t="n">
-        <v>80488</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455100</v>
+        <v>454969</v>
       </c>
       <c r="R29" t="n">
-        <v>6795418</v>
+        <v>6795402</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,38 +3642,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673097</t>
+          <t>https://artportalen.se/Sighting/135141340</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134673122</v>
+        <v>135613311</v>
       </c>
       <c r="B30" t="n">
-        <v>80488</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,17 +3682,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455113</v>
+        <v>455151</v>
       </c>
       <c r="R30" t="n">
-        <v>6795465</v>
+        <v>6795414</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,13 +3748,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673122</t>
+          <t>https://artportalen.se/Sighting/135613311</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135141238</v>
+        <v>134673097</v>
       </c>
       <c r="B31" t="n">
         <v>80488</v>
@@ -3788,17 +3788,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455104</v>
+        <v>455100</v>
       </c>
       <c r="R31" t="n">
-        <v>6795429</v>
+        <v>6795418</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3854,16 +3854,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135141238</t>
+          <t>https://artportalen.se/Sighting/134673097</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134614537</v>
+        <v>134673122</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,31 +3871,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3903,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455028</v>
+        <v>455113</v>
       </c>
       <c r="R32" t="n">
-        <v>6795330</v>
+        <v>6795465</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3933,12 +3928,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3947,6 +3942,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3964,16 +3960,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614537</t>
+          <t>https://artportalen.se/Sighting/134673122</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134626925</v>
+        <v>135141238</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>80526</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,31 +3977,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4013,13 +4004,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454878</v>
+        <v>455104</v>
       </c>
       <c r="R33" t="n">
-        <v>6795300</v>
+        <v>6795429</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4043,12 +4034,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4057,6 +4048,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4074,13 +4066,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134626925</t>
+          <t>https://artportalen.se/Sighting/135141238</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134627054</v>
+        <v>134614537</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -4123,10 +4115,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454812</v>
+        <v>455028</v>
       </c>
       <c r="R34" t="n">
-        <v>6795344</v>
+        <v>6795330</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4184,13 +4176,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627054</t>
+          <t>https://artportalen.se/Sighting/134614537</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134627301</v>
+        <v>134626925</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4229,14 +4221,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454942</v>
+        <v>454878</v>
       </c>
       <c r="R35" t="n">
-        <v>6795417</v>
+        <v>6795300</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4294,13 +4286,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627301</t>
+          <t>https://artportalen.se/Sighting/134626925</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134673183</v>
+        <v>134627054</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4339,14 +4331,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455102</v>
+        <v>454812</v>
       </c>
       <c r="R36" t="n">
-        <v>6795356</v>
+        <v>6795344</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4373,12 +4365,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4404,13 +4396,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673183</t>
+          <t>https://artportalen.se/Sighting/134627054</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134673244</v>
+        <v>134627301</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4443,7 +4435,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4453,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455111</v>
+        <v>454942</v>
       </c>
       <c r="R37" t="n">
-        <v>6795338</v>
+        <v>6795417</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4483,12 +4475,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4514,13 +4506,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673244</t>
+          <t>https://artportalen.se/Sighting/134627301</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134673280</v>
+        <v>134673183</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4559,14 +4551,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455026</v>
+        <v>455102</v>
       </c>
       <c r="R38" t="n">
-        <v>6795364</v>
+        <v>6795356</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4624,13 +4616,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673280</t>
+          <t>https://artportalen.se/Sighting/134673183</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134673340</v>
+        <v>134673244</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4663,7 +4655,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4673,10 +4665,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455035</v>
+        <v>455111</v>
       </c>
       <c r="R39" t="n">
-        <v>6795361</v>
+        <v>6795338</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4734,13 +4726,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673340</t>
+          <t>https://artportalen.se/Sighting/134673244</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134673359</v>
+        <v>134673280</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4773,20 +4765,20 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455183</v>
+        <v>455026</v>
       </c>
       <c r="R40" t="n">
-        <v>6795468</v>
+        <v>6795364</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4844,44 +4836,48 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673359</t>
+          <t>https://artportalen.se/Sighting/134673280</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134614645</v>
+        <v>134673340</v>
       </c>
       <c r="B41" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4889,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455028</v>
+        <v>455035</v>
       </c>
       <c r="R41" t="n">
-        <v>6795377</v>
+        <v>6795361</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4919,12 +4915,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4933,7 +4929,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4951,44 +4946,48 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614645</t>
+          <t>https://artportalen.se/Sighting/134673340</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134614705</v>
+        <v>134673359</v>
       </c>
       <c r="B42" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4996,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455116</v>
+        <v>455183</v>
       </c>
       <c r="R42" t="n">
-        <v>6795394</v>
+        <v>6795468</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5026,12 +5025,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5040,7 +5039,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5058,44 +5056,48 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614705</t>
+          <t>https://artportalen.se/Sighting/134673359</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134614735</v>
+        <v>135613442</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5103,13 +5105,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455163</v>
+        <v>455180</v>
       </c>
       <c r="R43" t="n">
-        <v>6795351</v>
+        <v>6795455</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5133,12 +5135,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringad tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5147,7 +5154,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5165,16 +5171,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614735</t>
+          <t>https://artportalen.se/Sighting/135613442</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134614754</v>
+        <v>135613281</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>57167</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5182,27 +5188,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5210,13 +5224,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455159</v>
+        <v>455256</v>
       </c>
       <c r="R44" t="n">
-        <v>6795377</v>
+        <v>6795475</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5240,12 +5254,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5254,7 +5268,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5272,13 +5285,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614754</t>
+          <t>https://artportalen.se/Sighting/135613281</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134627237</v>
+        <v>134614645</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5317,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454916</v>
+        <v>455028</v>
       </c>
       <c r="R45" t="n">
-        <v>6795349</v>
+        <v>6795377</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5379,16 +5392,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627237</t>
+          <t>https://artportalen.se/Sighting/134614645</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134614906</v>
+        <v>134614705</v>
       </c>
       <c r="B46" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5396,21 +5409,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5424,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455317</v>
+        <v>455116</v>
       </c>
       <c r="R46" t="n">
-        <v>6795637</v>
+        <v>6795394</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5486,16 +5499,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614906</t>
+          <t>https://artportalen.se/Sighting/134614705</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134627179</v>
+        <v>134614735</v>
       </c>
       <c r="B47" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5503,21 +5516,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5531,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454911</v>
+        <v>455163</v>
       </c>
       <c r="R47" t="n">
-        <v>6795314</v>
+        <v>6795351</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5593,16 +5606,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627179</t>
+          <t>https://artportalen.se/Sighting/134614735</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134627242</v>
+        <v>134614754</v>
       </c>
       <c r="B48" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5610,21 +5623,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5638,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454916</v>
+        <v>455159</v>
       </c>
       <c r="R48" t="n">
-        <v>6795349</v>
+        <v>6795377</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5700,16 +5713,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627242</t>
+          <t>https://artportalen.se/Sighting/134614754</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134627258</v>
+        <v>134627237</v>
       </c>
       <c r="B49" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5717,21 +5730,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5745,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454930</v>
+        <v>454916</v>
       </c>
       <c r="R49" t="n">
-        <v>6795363</v>
+        <v>6795349</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5807,16 +5820,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627258</t>
+          <t>https://artportalen.se/Sighting/134627237</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134614664</v>
+        <v>134614906</v>
       </c>
       <c r="B50" t="n">
-        <v>99217</v>
+        <v>99099</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5824,21 +5837,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5852,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455110</v>
+        <v>455317</v>
       </c>
       <c r="R50" t="n">
-        <v>6795376</v>
+        <v>6795637</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5914,42 +5927,50 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614664</t>
+          <t>https://artportalen.se/Sighting/134614906</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134614688</v>
+        <v>135613353</v>
       </c>
       <c r="B51" t="n">
-        <v>99217</v>
+        <v>99242</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -5959,13 +5980,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455116</v>
+        <v>455091</v>
       </c>
       <c r="R51" t="n">
-        <v>6795380</v>
+        <v>6795402</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5989,12 +6010,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6021,42 +6042,50 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614688</t>
+          <t>https://artportalen.se/Sighting/135613353</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134614788</v>
+        <v>135613480</v>
       </c>
       <c r="B52" t="n">
-        <v>99217</v>
+        <v>99242</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6066,13 +6095,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455170</v>
+        <v>454890</v>
       </c>
       <c r="R52" t="n">
-        <v>6795392</v>
+        <v>6795270</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6096,12 +6125,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6128,42 +6157,50 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614788</t>
+          <t>https://artportalen.se/Sighting/135613480</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134614819</v>
+        <v>135613539</v>
       </c>
       <c r="B53" t="n">
-        <v>99217</v>
+        <v>99242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6173,13 +6210,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455188</v>
+        <v>454911</v>
       </c>
       <c r="R53" t="n">
-        <v>6795401</v>
+        <v>6795328</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6203,12 +6240,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6235,42 +6272,50 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614819</t>
+          <t>https://artportalen.se/Sighting/135613539</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134614899</v>
+        <v>135613546</v>
       </c>
       <c r="B54" t="n">
-        <v>99217</v>
+        <v>99242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6280,13 +6325,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455327</v>
+        <v>454906</v>
       </c>
       <c r="R54" t="n">
-        <v>6795641</v>
+        <v>6795301</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6310,12 +6355,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6342,16 +6387,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614899</t>
+          <t>https://artportalen.se/Sighting/135613546</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134627270</v>
+        <v>134627179</v>
       </c>
       <c r="B55" t="n">
-        <v>99217</v>
+        <v>109924</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6359,21 +6404,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>221184</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6387,10 +6432,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454933</v>
+        <v>454911</v>
       </c>
       <c r="R55" t="n">
-        <v>6795362</v>
+        <v>6795314</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6449,16 +6494,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627270</t>
+          <t>https://artportalen.se/Sighting/134627179</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135141343</v>
+        <v>134627242</v>
       </c>
       <c r="B56" t="n">
-        <v>99217</v>
+        <v>109924</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6466,21 +6511,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>221184</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6494,13 +6539,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454969</v>
+        <v>454916</v>
       </c>
       <c r="R56" t="n">
-        <v>6795402</v>
+        <v>6795349</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6524,12 +6569,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6555,6 +6600,862 @@
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627242</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134627258</v>
+      </c>
+      <c r="B57" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>454930</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6795363</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627258</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134614664</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>455110</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6795376</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614664</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134614688</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>455116</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6795380</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614688</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134614788</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>455170</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6795392</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614788</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134614819</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>455188</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6795401</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614819</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134614899</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>455327</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6795641</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614899</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134627270</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>454933</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6795362</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627270</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135141343</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99264</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>454969</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6795402</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135141343</t>
         </is>
@@ -6617,6 +7518,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135613306</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>135141304</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>135141324</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>135141340</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>135613311</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>135141238</v>
       </c>
       <c r="B33" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>135613353</v>
       </c>
       <c r="B51" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135613480</v>
       </c>
       <c r="B52" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>135613539</v>
       </c>
       <c r="B53" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135613546</v>
       </c>
       <c r="B54" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>135141343</v>
       </c>
       <c r="B64" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134614586</v>
+        <v>135613306</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,17 +820,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455034</v>
+        <v>455151</v>
       </c>
       <c r="R3" t="n">
-        <v>6795328</v>
+        <v>6795414</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,13 +886,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614586</t>
+          <t>https://artportalen.se/Sighting/135613306</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134614602</v>
+        <v>134614586</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -926,14 +926,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455012</v>
+        <v>455034</v>
       </c>
       <c r="R4" t="n">
-        <v>6795340</v>
+        <v>6795328</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,13 +992,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614602</t>
+          <t>https://artportalen.se/Sighting/134614586</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134614617</v>
+        <v>134614602</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455021</v>
+        <v>455012</v>
       </c>
       <c r="R5" t="n">
-        <v>6795317</v>
+        <v>6795340</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,13 +1098,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614617</t>
+          <t>https://artportalen.se/Sighting/134614602</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134614692</v>
+        <v>134614617</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455116</v>
+        <v>455021</v>
       </c>
       <c r="R6" t="n">
-        <v>6795380</v>
+        <v>6795317</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,13 +1204,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614692</t>
+          <t>https://artportalen.se/Sighting/134614617</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134614778</v>
+        <v>134614692</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455170</v>
+        <v>455116</v>
       </c>
       <c r="R7" t="n">
-        <v>6795392</v>
+        <v>6795380</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,13 +1310,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614778</t>
+          <t>https://artportalen.se/Sighting/134614692</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134614823</v>
+        <v>134614778</v>
       </c>
       <c r="B8" t="n">
         <v>79373</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455188</v>
+        <v>455170</v>
       </c>
       <c r="R8" t="n">
-        <v>6795401</v>
+        <v>6795392</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1416,13 +1416,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614823</t>
+          <t>https://artportalen.se/Sighting/134614778</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134614834</v>
+        <v>134614823</v>
       </c>
       <c r="B9" t="n">
         <v>79373</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455246</v>
+        <v>455188</v>
       </c>
       <c r="R9" t="n">
-        <v>6795421</v>
+        <v>6795401</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1522,13 +1522,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614834</t>
+          <t>https://artportalen.se/Sighting/134614823</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134614839</v>
+        <v>134614834</v>
       </c>
       <c r="B10" t="n">
         <v>79373</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455282</v>
+        <v>455246</v>
       </c>
       <c r="R10" t="n">
-        <v>6795462</v>
+        <v>6795421</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1628,13 +1628,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614839</t>
+          <t>https://artportalen.se/Sighting/134614834</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134614845</v>
+        <v>134614839</v>
       </c>
       <c r="B11" t="n">
         <v>79373</v>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455254</v>
+        <v>455282</v>
       </c>
       <c r="R11" t="n">
-        <v>6795551</v>
+        <v>6795462</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1734,13 +1734,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614845</t>
+          <t>https://artportalen.se/Sighting/134614839</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134614867</v>
+        <v>134614845</v>
       </c>
       <c r="B12" t="n">
         <v>79373</v>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455274</v>
+        <v>455254</v>
       </c>
       <c r="R12" t="n">
-        <v>6795546</v>
+        <v>6795551</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1840,13 +1840,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614867</t>
+          <t>https://artportalen.se/Sighting/134614845</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134614878</v>
+        <v>134614867</v>
       </c>
       <c r="B13" t="n">
         <v>79373</v>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455305</v>
+        <v>455274</v>
       </c>
       <c r="R13" t="n">
-        <v>6795540</v>
+        <v>6795546</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1946,13 +1946,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614878</t>
+          <t>https://artportalen.se/Sighting/134614867</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134614890</v>
+        <v>134614878</v>
       </c>
       <c r="B14" t="n">
         <v>79373</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455327</v>
+        <v>455305</v>
       </c>
       <c r="R14" t="n">
-        <v>6795641</v>
+        <v>6795540</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,13 +2052,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614890</t>
+          <t>https://artportalen.se/Sighting/134614878</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134614909</v>
+        <v>134614890</v>
       </c>
       <c r="B15" t="n">
         <v>79373</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455317</v>
+        <v>455327</v>
       </c>
       <c r="R15" t="n">
-        <v>6795637</v>
+        <v>6795641</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2158,13 +2158,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614909</t>
+          <t>https://artportalen.se/Sighting/134614890</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134614972</v>
+        <v>134614909</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455066</v>
+        <v>455317</v>
       </c>
       <c r="R16" t="n">
-        <v>6795462</v>
+        <v>6795637</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2264,13 +2264,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614972</t>
+          <t>https://artportalen.se/Sighting/134614909</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134614977</v>
+        <v>134614972</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455076</v>
+        <v>455066</v>
       </c>
       <c r="R17" t="n">
-        <v>6795492</v>
+        <v>6795462</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2370,13 +2370,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614977</t>
+          <t>https://artportalen.se/Sighting/134614972</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134614988</v>
+        <v>134614977</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455095</v>
+        <v>455076</v>
       </c>
       <c r="R18" t="n">
-        <v>6795496</v>
+        <v>6795492</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2476,13 +2476,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614988</t>
+          <t>https://artportalen.se/Sighting/134614977</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134627106</v>
+        <v>134614988</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2516,14 +2516,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454812</v>
+        <v>455095</v>
       </c>
       <c r="R19" t="n">
-        <v>6795344</v>
+        <v>6795496</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2582,13 +2582,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627106</t>
+          <t>https://artportalen.se/Sighting/134614988</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134627119</v>
+        <v>134627106</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454878</v>
+        <v>454812</v>
       </c>
       <c r="R20" t="n">
-        <v>6795300</v>
+        <v>6795344</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2688,13 +2688,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627119</t>
+          <t>https://artportalen.se/Sighting/134627106</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134627145</v>
+        <v>134627119</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454848</v>
+        <v>454878</v>
       </c>
       <c r="R21" t="n">
-        <v>6795313</v>
+        <v>6795300</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2794,13 +2794,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627145</t>
+          <t>https://artportalen.se/Sighting/134627119</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134627160</v>
+        <v>134627145</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2834,14 +2834,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454866</v>
+        <v>454848</v>
       </c>
       <c r="R22" t="n">
-        <v>6795380</v>
+        <v>6795313</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2900,13 +2900,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627160</t>
+          <t>https://artportalen.se/Sighting/134627145</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134627309</v>
+        <v>134627160</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454942</v>
+        <v>454866</v>
       </c>
       <c r="R23" t="n">
-        <v>6795417</v>
+        <v>6795380</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3006,13 +3006,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627309</t>
+          <t>https://artportalen.se/Sighting/134627160</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134627464</v>
+        <v>134627309</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454917</v>
+        <v>454942</v>
       </c>
       <c r="R24" t="n">
-        <v>6795398</v>
+        <v>6795417</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3112,13 +3112,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627464</t>
+          <t>https://artportalen.se/Sighting/134627309</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134673366</v>
+        <v>134627464</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455114</v>
+        <v>454917</v>
       </c>
       <c r="R25" t="n">
-        <v>6795450</v>
+        <v>6795398</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,16 +3218,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673366</t>
+          <t>https://artportalen.se/Sighting/134627464</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135141304</v>
+        <v>134673366</v>
       </c>
       <c r="B26" t="n">
-        <v>79438</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455021</v>
+        <v>455114</v>
       </c>
       <c r="R26" t="n">
-        <v>6795446</v>
+        <v>6795450</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3324,13 +3324,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135141304</t>
+          <t>https://artportalen.se/Sighting/134673366</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135141324</v>
+        <v>135141304</v>
       </c>
       <c r="B27" t="n">
         <v>79438</v>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455053</v>
+        <v>455021</v>
       </c>
       <c r="R27" t="n">
-        <v>6795452</v>
+        <v>6795446</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,13 +3430,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135141324</t>
+          <t>https://artportalen.se/Sighting/135141304</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135141340</v>
+        <v>135141324</v>
       </c>
       <c r="B28" t="n">
         <v>79438</v>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454969</v>
+        <v>455053</v>
       </c>
       <c r="R28" t="n">
-        <v>6795402</v>
+        <v>6795452</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,38 +3536,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135141340</t>
+          <t>https://artportalen.se/Sighting/135141324</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134673097</v>
+        <v>135141340</v>
       </c>
       <c r="B29" t="n">
-        <v>80488</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455100</v>
+        <v>454969</v>
       </c>
       <c r="R29" t="n">
-        <v>6795418</v>
+        <v>6795402</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,38 +3642,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673097</t>
+          <t>https://artportalen.se/Sighting/135141340</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134673122</v>
+        <v>135613311</v>
       </c>
       <c r="B30" t="n">
-        <v>80488</v>
+        <v>79441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,17 +3682,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455113</v>
+        <v>455151</v>
       </c>
       <c r="R30" t="n">
-        <v>6795465</v>
+        <v>6795414</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,16 +3748,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673122</t>
+          <t>https://artportalen.se/Sighting/135613311</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135141238</v>
+        <v>134673097</v>
       </c>
       <c r="B31" t="n">
-        <v>80553</v>
+        <v>80488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3788,17 +3788,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455104</v>
+        <v>455100</v>
       </c>
       <c r="R31" t="n">
-        <v>6795429</v>
+        <v>6795418</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3854,16 +3854,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135141238</t>
+          <t>https://artportalen.se/Sighting/134673097</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134614537</v>
+        <v>134673122</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3871,31 +3871,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3903,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455028</v>
+        <v>455113</v>
       </c>
       <c r="R32" t="n">
-        <v>6795330</v>
+        <v>6795465</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3933,12 +3928,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3947,6 +3942,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3964,16 +3960,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614537</t>
+          <t>https://artportalen.se/Sighting/134673122</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134626925</v>
+        <v>135141238</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>80553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3981,31 +3977,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4013,13 +4004,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454878</v>
+        <v>455104</v>
       </c>
       <c r="R33" t="n">
-        <v>6795300</v>
+        <v>6795429</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4043,12 +4034,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4057,6 +4048,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4074,13 +4066,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134626925</t>
+          <t>https://artportalen.se/Sighting/135141238</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134627054</v>
+        <v>134614537</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -4123,10 +4115,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454812</v>
+        <v>455028</v>
       </c>
       <c r="R34" t="n">
-        <v>6795344</v>
+        <v>6795330</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4184,13 +4176,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627054</t>
+          <t>https://artportalen.se/Sighting/134614537</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134627301</v>
+        <v>134626925</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4229,14 +4221,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454942</v>
+        <v>454878</v>
       </c>
       <c r="R35" t="n">
-        <v>6795417</v>
+        <v>6795300</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4294,13 +4286,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627301</t>
+          <t>https://artportalen.se/Sighting/134626925</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134673183</v>
+        <v>134627054</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4339,14 +4331,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455102</v>
+        <v>454812</v>
       </c>
       <c r="R36" t="n">
-        <v>6795356</v>
+        <v>6795344</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4373,12 +4365,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4404,13 +4396,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673183</t>
+          <t>https://artportalen.se/Sighting/134627054</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134673244</v>
+        <v>134627301</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4443,7 +4435,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4453,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455111</v>
+        <v>454942</v>
       </c>
       <c r="R37" t="n">
-        <v>6795338</v>
+        <v>6795417</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4483,12 +4475,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4514,13 +4506,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673244</t>
+          <t>https://artportalen.se/Sighting/134627301</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134673280</v>
+        <v>134673183</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4559,14 +4551,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
+          <t>Manmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455026</v>
+        <v>455102</v>
       </c>
       <c r="R38" t="n">
-        <v>6795364</v>
+        <v>6795356</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4624,13 +4616,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673280</t>
+          <t>https://artportalen.se/Sighting/134673183</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134673340</v>
+        <v>134673244</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4663,7 +4655,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4673,10 +4665,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455035</v>
+        <v>455111</v>
       </c>
       <c r="R39" t="n">
-        <v>6795361</v>
+        <v>6795338</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4734,13 +4726,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673340</t>
+          <t>https://artportalen.se/Sighting/134673244</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134673359</v>
+        <v>134673280</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4773,20 +4765,20 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Manmyrbäck, Dlr</t>
+          <t>Manmyrbäck, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455183</v>
+        <v>455026</v>
       </c>
       <c r="R40" t="n">
-        <v>6795468</v>
+        <v>6795364</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4844,44 +4836,48 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134673359</t>
+          <t>https://artportalen.se/Sighting/134673280</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134614645</v>
+        <v>134673340</v>
       </c>
       <c r="B41" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4889,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455028</v>
+        <v>455035</v>
       </c>
       <c r="R41" t="n">
-        <v>6795377</v>
+        <v>6795361</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4919,12 +4915,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4933,7 +4929,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4951,44 +4946,48 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614645</t>
+          <t>https://artportalen.se/Sighting/134673340</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134614705</v>
+        <v>134673359</v>
       </c>
       <c r="B42" t="n">
-        <v>99112</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4996,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455116</v>
+        <v>455183</v>
       </c>
       <c r="R42" t="n">
-        <v>6795394</v>
+        <v>6795468</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5026,12 +5025,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5040,7 +5039,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5058,44 +5056,48 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614705</t>
+          <t>https://artportalen.se/Sighting/134673359</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134614735</v>
+        <v>135613442</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5103,13 +5105,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455163</v>
+        <v>455180</v>
       </c>
       <c r="R43" t="n">
-        <v>6795351</v>
+        <v>6795455</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5133,12 +5135,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringad tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5147,7 +5154,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5165,16 +5171,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614735</t>
+          <t>https://artportalen.se/Sighting/135613442</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134614754</v>
+        <v>135613281</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>57167</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5182,27 +5188,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5210,13 +5224,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455159</v>
+        <v>455256</v>
       </c>
       <c r="R44" t="n">
-        <v>6795377</v>
+        <v>6795475</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5240,12 +5254,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5254,7 +5268,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5272,13 +5285,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614754</t>
+          <t>https://artportalen.se/Sighting/135613281</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134627237</v>
+        <v>134614645</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5317,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454916</v>
+        <v>455028</v>
       </c>
       <c r="R45" t="n">
-        <v>6795349</v>
+        <v>6795377</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5379,16 +5392,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627237</t>
+          <t>https://artportalen.se/Sighting/134614645</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134614906</v>
+        <v>134614705</v>
       </c>
       <c r="B46" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5396,21 +5409,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5424,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455317</v>
+        <v>455116</v>
       </c>
       <c r="R46" t="n">
-        <v>6795637</v>
+        <v>6795394</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5486,16 +5499,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614906</t>
+          <t>https://artportalen.se/Sighting/134614705</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134627179</v>
+        <v>134614735</v>
       </c>
       <c r="B47" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5503,21 +5516,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5531,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>454911</v>
+        <v>455163</v>
       </c>
       <c r="R47" t="n">
-        <v>6795314</v>
+        <v>6795351</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5593,16 +5606,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627179</t>
+          <t>https://artportalen.se/Sighting/134614735</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134627242</v>
+        <v>134614754</v>
       </c>
       <c r="B48" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5610,21 +5623,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5638,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454916</v>
+        <v>455159</v>
       </c>
       <c r="R48" t="n">
-        <v>6795349</v>
+        <v>6795377</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5700,16 +5713,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627242</t>
+          <t>https://artportalen.se/Sighting/134614754</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134627258</v>
+        <v>134627237</v>
       </c>
       <c r="B49" t="n">
-        <v>109924</v>
+        <v>99112</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5717,21 +5730,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221184</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5745,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454930</v>
+        <v>454916</v>
       </c>
       <c r="R49" t="n">
-        <v>6795363</v>
+        <v>6795349</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5807,16 +5820,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627258</t>
+          <t>https://artportalen.se/Sighting/134627237</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134614664</v>
+        <v>134614906</v>
       </c>
       <c r="B50" t="n">
-        <v>99217</v>
+        <v>99099</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5824,21 +5837,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5852,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455110</v>
+        <v>455317</v>
       </c>
       <c r="R50" t="n">
-        <v>6795376</v>
+        <v>6795637</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5914,42 +5927,50 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614664</t>
+          <t>https://artportalen.se/Sighting/134614906</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134614688</v>
+        <v>135613353</v>
       </c>
       <c r="B51" t="n">
-        <v>99217</v>
+        <v>99274</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -5959,13 +5980,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455116</v>
+        <v>455091</v>
       </c>
       <c r="R51" t="n">
-        <v>6795380</v>
+        <v>6795402</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5989,12 +6010,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6021,42 +6042,50 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614688</t>
+          <t>https://artportalen.se/Sighting/135613353</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134614788</v>
+        <v>135613480</v>
       </c>
       <c r="B52" t="n">
-        <v>99217</v>
+        <v>99274</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6066,13 +6095,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455170</v>
+        <v>454890</v>
       </c>
       <c r="R52" t="n">
-        <v>6795392</v>
+        <v>6795270</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6096,12 +6125,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6128,42 +6157,50 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614788</t>
+          <t>https://artportalen.se/Sighting/135613480</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134614819</v>
+        <v>135613539</v>
       </c>
       <c r="B53" t="n">
-        <v>99217</v>
+        <v>99274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6173,13 +6210,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>455188</v>
+        <v>454911</v>
       </c>
       <c r="R53" t="n">
-        <v>6795401</v>
+        <v>6795328</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6203,12 +6240,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6235,42 +6272,50 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614819</t>
+          <t>https://artportalen.se/Sighting/135613539</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134614899</v>
+        <v>135613546</v>
       </c>
       <c r="B54" t="n">
-        <v>99217</v>
+        <v>99274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6280,13 +6325,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>455327</v>
+        <v>454906</v>
       </c>
       <c r="R54" t="n">
-        <v>6795641</v>
+        <v>6795301</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6310,12 +6355,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6342,16 +6387,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134614899</t>
+          <t>https://artportalen.se/Sighting/135613546</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134627270</v>
+        <v>134627179</v>
       </c>
       <c r="B55" t="n">
-        <v>99217</v>
+        <v>109924</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6359,21 +6404,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>221184</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6387,10 +6432,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>454933</v>
+        <v>454911</v>
       </c>
       <c r="R55" t="n">
-        <v>6795362</v>
+        <v>6795314</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6449,16 +6494,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134627270</t>
+          <t>https://artportalen.se/Sighting/134627179</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135141343</v>
+        <v>134627242</v>
       </c>
       <c r="B56" t="n">
-        <v>99291</v>
+        <v>109924</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6466,21 +6511,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>221184</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6494,13 +6539,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>454969</v>
+        <v>454916</v>
       </c>
       <c r="R56" t="n">
-        <v>6795402</v>
+        <v>6795349</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6524,12 +6569,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6555,6 +6600,862 @@
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627242</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134627258</v>
+      </c>
+      <c r="B57" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>454930</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6795363</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627258</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134614664</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>455110</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6795376</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614664</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134614688</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>455116</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6795380</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614688</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134614788</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>455170</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6795392</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614788</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134614819</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>455188</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6795401</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614819</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134614899</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>455327</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6795641</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134614899</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134627270</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>454933</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6795362</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134627270</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135141343</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99291</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Manmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>454969</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6795402</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135141343</t>
         </is>
@@ -6617,6 +7518,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -5936,7 +5936,7 @@
         <v>135613353</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135613480</v>
       </c>
       <c r="B52" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>135613539</v>
       </c>
       <c r="B53" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135613546</v>
       </c>
       <c r="B54" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135613306</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>135613311</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>135613442</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>135613281</v>
       </c>
       <c r="B44" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>135613353</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135613480</v>
       </c>
       <c r="B52" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>135613539</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135613546</v>
       </c>
       <c r="B54" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135613306</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>135613311</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>135613353</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135613480</v>
       </c>
       <c r="B52" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>135613539</v>
       </c>
       <c r="B53" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135613546</v>
       </c>
       <c r="B54" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -5936,7 +5936,7 @@
         <v>135613353</v>
       </c>
       <c r="B51" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135613480</v>
       </c>
       <c r="B52" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>135613539</v>
       </c>
       <c r="B53" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135613546</v>
       </c>
       <c r="B54" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 45783-2022 artfynd.xlsx
+++ b/artfynd/A 45783-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135613306</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>135613311</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>135613442</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>135613281</v>
       </c>
       <c r="B44" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>135613353</v>
       </c>
       <c r="B51" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135613480</v>
       </c>
       <c r="B52" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>135613539</v>
       </c>
       <c r="B53" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>135613546</v>
       </c>
       <c r="B54" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
